--- a/Result/profitability/1605.xlsx
+++ b/Result/profitability/1605.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.21</v>
+        <v>0.45375</v>
       </c>
       <c r="N2" t="n">
-        <v>6.05375</v>
+        <v>6.26125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.18</v>
       </c>
       <c r="M3" t="n">
-        <v>0.22125</v>
+        <v>0.4950000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>5.825</v>
+        <v>6.09875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>-0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0.205</v>
+        <v>0.43875</v>
       </c>
       <c r="N4" t="n">
-        <v>5.34125</v>
+        <v>5.255000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.64</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02124999999999996</v>
+        <v>0.2187500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>3.60125</v>
+        <v>3.635</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03374999999999995</v>
+        <v>0.1925000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1675</v>
+        <v>4.5175</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03249999999999996</v>
+        <v>0.1925000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>4.49875</v>
+        <v>4.831250000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03749999999999995</v>
+        <v>0.11625</v>
       </c>
       <c r="N8" t="n">
-        <v>4.79</v>
+        <v>4.76375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2031,7 +2031,7 @@
         <v>0.2525000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>6.18375</v>
+        <v>6.183750000000001</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>49648</v>
+      </c>
+      <c r="D75" t="n">
+        <v>45895</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3753</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="G75" t="n">
+        <v>726</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8387</v>
+      </c>
+      <c r="J75" t="n">
+        <v>9113</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9043</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.44375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.518518518518519</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02702702702702697</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.2699999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.03703703703703698</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
